--- a/docs/templates/supernova_content_template.xlsx
+++ b/docs/templates/supernova_content_template.xlsx
@@ -131,7 +131,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1202,7 +1204,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Last one — put it all together. Give a full introduction: your name, where you're from, what you do, and one interest.</t>
+          <t>Last one — put it all together. Give a full introduction: your name, where you’re from, what you do, and one interest.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
